--- a/Config/Luban/Datas/__tables__.xlsx
+++ b/Config/Luban/Datas/__tables__.xlsx
@@ -416,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K5"/>
+  <dimension ref="A1:K8"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col width="20.375" customWidth="1" style="2" min="2" max="2"/>
@@ -575,12 +575,12 @@
     <row r="4">
       <c r="B4" t="inlineStr">
         <is>
-          <t>TbCharacter</t>
+          <t>TbItem</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Character</t>
+          <t>Item</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -590,7 +590,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Character@Gameplay.xlsx</t>
+          <t>Item@Gameplay.xlsx</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
@@ -602,53 +602,161 @@
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr">
         <is>
-          <t>角色基础生命（玩家/敌人/Boss 共用，主键=角色配置ID）</t>
+          <t>物品与武器基础数值（背包/商店/伤害链路共用）</t>
         </is>
       </c>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr">
         <is>
-          <t>character</t>
+          <t>item</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="B5" t="inlineStr">
         <is>
+          <t>TbCharacter</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Character</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Character@Gameplay.xlsx</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>map</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>角色基础生命（玩家/敌人/Boss 共用，主键=角色配置ID）</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>character</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>TbPlayer</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Player</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Player@Gameplay.xlsx</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>map</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>玩家移动/翻滚/锁定手感数值</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>player</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="B7" t="inlineStr">
+        <is>
           <t>TbStamina</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C7" t="inlineStr">
         <is>
           <t>Stamina</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="D7" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="E7" t="inlineStr">
         <is>
           <t>Stamina@Gameplay.xlsx</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr">
+      <c r="G7" t="inlineStr">
         <is>
           <t>map</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr"/>
-      <c r="I5" t="inlineStr">
+      <c r="I7" t="inlineStr">
         <is>
           <t>耐力配置（玩家/敌人共用，主键引用 Character.id）</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr">
+      <c r="K7" t="inlineStr">
         <is>
           <t>stamina</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>TbParry</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Parry</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Parry@Gameplay.xlsx</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>map</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>弹反/格挡数值（未启用功能的开发初始值）</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>parry</t>
         </is>
       </c>
     </row>

--- a/Config/Luban/Datas/__tables__.xlsx
+++ b/Config/Luban/Datas/__tables__.xlsx
@@ -416,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K8"/>
+  <dimension ref="A1:K10"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col width="20.375" customWidth="1" style="2" min="2" max="2"/>
@@ -575,12 +575,12 @@
     <row r="4">
       <c r="B4" t="inlineStr">
         <is>
-          <t>TbItem</t>
+          <t>TbWeapon</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Item</t>
+          <t>Weapon</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -590,7 +590,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Item@Gameplay.xlsx</t>
+          <t>Weapon@Gameplay.xlsx</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
@@ -602,25 +602,25 @@
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr">
         <is>
-          <t>物品与武器基础数值（背包/商店/伤害链路共用）</t>
+          <t>武器数值（攻击距离/弹药/冷却/弹速/散布）</t>
         </is>
       </c>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr">
         <is>
-          <t>item</t>
+          <t>weapon</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="B5" t="inlineStr">
         <is>
-          <t>TbCharacter</t>
+          <t>TbWeaponUpgrade</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Character</t>
+          <t>WeaponUpgrade</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -630,34 +630,37 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Character@Gameplay.xlsx</t>
-        </is>
-      </c>
+          <t>WeaponUpgrade@Gameplay.xlsx</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>map</t>
-        </is>
-      </c>
+          <t>one</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr">
         <is>
-          <t>角色基础生命（玩家/敌人/Boss 共用，主键=角色配置ID）</t>
-        </is>
-      </c>
+          <t>武器升级上限与系数（单行表）</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr">
         <is>
-          <t>character</t>
+          <t>weapon_upgrade</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="B6" t="inlineStr">
         <is>
-          <t>TbPlayer</t>
+          <t>TbItem</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Player</t>
+          <t>Item</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -667,7 +670,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Player@Gameplay.xlsx</t>
+          <t>Item@Gameplay.xlsx</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -677,24 +680,24 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>玩家移动/翻滚/锁定手感数值</t>
+          <t>物品与武器基础数值（背包/商店/伤害链路共用）</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>player</t>
+          <t>item</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="B7" t="inlineStr">
         <is>
-          <t>TbStamina</t>
+          <t>TbCharacter</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Stamina</t>
+          <t>Character</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -704,7 +707,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Stamina@Gameplay.xlsx</t>
+          <t>Character@Gameplay.xlsx</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -714,47 +717,121 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>耐力配置（玩家/敌人共用，主键引用 Character.id）</t>
+          <t>角色基础生命（玩家/敌人/Boss 共用，主键=角色配置ID）</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>stamina</t>
+          <t>character</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="B8" t="inlineStr">
         <is>
+          <t>TbPlayer</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Player</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Player@Gameplay.xlsx</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>map</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>玩家移动/翻滚/锁定手感数值</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>player</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>TbStamina</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Stamina</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Stamina@Gameplay.xlsx</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>map</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>耐力配置（玩家/敌人共用，主键引用 Character.id）</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>stamina</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="B10" t="inlineStr">
+        <is>
           <t>TbParry</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="C10" t="inlineStr">
         <is>
           <t>Parry</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="D10" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="E10" t="inlineStr">
         <is>
           <t>Parry@Gameplay.xlsx</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="G10" t="inlineStr">
         <is>
           <t>map</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr">
+      <c r="I10" t="inlineStr">
         <is>
           <t>弹反/格挡数值（未启用功能的开发初始值）</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr">
+      <c r="K10" t="inlineStr">
         <is>
           <t>parry</t>
         </is>

--- a/Config/Luban/Datas/__tables__.xlsx
+++ b/Config/Luban/Datas/__tables__.xlsx
@@ -416,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K10"/>
+  <dimension ref="A1:K11"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col width="20.375" customWidth="1" style="2" min="2" max="2"/>
@@ -575,12 +575,12 @@
     <row r="4">
       <c r="B4" t="inlineStr">
         <is>
-          <t>TbWeapon</t>
+          <t>TbAttack</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Weapon</t>
+          <t>Attack</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -590,7 +590,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Weapon@Gameplay.xlsx</t>
+          <t>Attack@Gameplay.xlsx</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
@@ -602,25 +602,25 @@
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr">
         <is>
-          <t>武器数值（攻击距离/弹药/冷却/弹速/散布）</t>
+          <t>所有招式数值（玩家/敌人共用，主键=AttackData 的稳定 attackId）</t>
         </is>
       </c>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr">
         <is>
-          <t>weapon</t>
+          <t>attack</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="B5" t="inlineStr">
         <is>
-          <t>TbWeaponUpgrade</t>
+          <t>TbWeapon</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>WeaponUpgrade</t>
+          <t>Weapon</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -630,37 +630,34 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>WeaponUpgrade@Gameplay.xlsx</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr"/>
+          <t>Weapon@Gameplay.xlsx</t>
+        </is>
+      </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>one</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr"/>
+          <t>map</t>
+        </is>
+      </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>武器升级上限与系数（单行表）</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr"/>
+          <t>武器数值（攻击距离/弹药/冷却/弹速/散布）</t>
+        </is>
+      </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>weapon_upgrade</t>
+          <t>weapon</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="B6" t="inlineStr">
         <is>
-          <t>TbItem</t>
+          <t>TbWeaponUpgrade</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Item</t>
+          <t>WeaponUpgrade</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -670,34 +667,34 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Item@Gameplay.xlsx</t>
+          <t>WeaponUpgrade@Gameplay.xlsx</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>map</t>
+          <t>one</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>物品与武器基础数值（背包/商店/伤害链路共用）</t>
+          <t>武器升级上限与系数（单行表）</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>item</t>
+          <t>weapon_upgrade</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="B7" t="inlineStr">
         <is>
-          <t>TbCharacter</t>
+          <t>TbItem</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Character</t>
+          <t>Item</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -707,7 +704,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Character@Gameplay.xlsx</t>
+          <t>Item@Gameplay.xlsx</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -717,24 +714,24 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>角色基础生命（玩家/敌人/Boss 共用，主键=角色配置ID）</t>
+          <t>物品与武器基础数值（背包/商店/伤害链路共用）</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>character</t>
+          <t>item</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="B8" t="inlineStr">
         <is>
-          <t>TbPlayer</t>
+          <t>TbCharacter</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Player</t>
+          <t>Character</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -744,7 +741,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Player@Gameplay.xlsx</t>
+          <t>Character@Gameplay.xlsx</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -754,24 +751,24 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>玩家移动/翻滚/锁定手感数值</t>
+          <t>角色基础生命（玩家/敌人/Boss 共用，主键=角色配置ID）</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>player</t>
+          <t>character</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="B9" t="inlineStr">
         <is>
-          <t>TbStamina</t>
+          <t>TbPlayer</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Stamina</t>
+          <t>Player</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -781,7 +778,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Stamina@Gameplay.xlsx</t>
+          <t>Player@Gameplay.xlsx</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -791,47 +788,84 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>耐力配置（玩家/敌人共用，主键引用 Character.id）</t>
+          <t>玩家移动/翻滚/锁定手感数值</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>stamina</t>
+          <t>player</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="B10" t="inlineStr">
         <is>
+          <t>TbStamina</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Stamina</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Stamina@Gameplay.xlsx</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>map</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>耐力配置（玩家/敌人共用，主键引用 Character.id）</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>stamina</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="B11" t="inlineStr">
+        <is>
           <t>TbParry</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="C11" t="inlineStr">
         <is>
           <t>Parry</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="D11" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="E11" t="inlineStr">
         <is>
           <t>Parry@Gameplay.xlsx</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
+      <c r="G11" t="inlineStr">
         <is>
           <t>map</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr">
+      <c r="I11" t="inlineStr">
         <is>
           <t>弹反/格挡数值（未启用功能的开发初始值）</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr">
+      <c r="K11" t="inlineStr">
         <is>
           <t>parry</t>
         </is>

--- a/Config/Luban/Datas/__tables__.xlsx
+++ b/Config/Luban/Datas/__tables__.xlsx
@@ -416,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K11"/>
+  <dimension ref="A1:K12"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col width="20.375" customWidth="1" style="2" min="2" max="2"/>
@@ -575,12 +575,12 @@
     <row r="4">
       <c r="B4" t="inlineStr">
         <is>
-          <t>TbAttack</t>
+          <t>TbCombatGlobal</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Attack</t>
+          <t>CombatGlobal</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -590,37 +590,37 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Attack@Gameplay.xlsx</t>
+          <t>CombatGlobal@Gameplay.xlsx</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>map</t>
+          <t>one</t>
         </is>
       </c>
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr">
         <is>
-          <t>所有招式数值（玩家/敌人共用，主键=AttackData 的稳定 attackId）</t>
+          <t>全局战斗默认值：兜底伤害与卡肉参数（单行表）</t>
         </is>
       </c>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr">
         <is>
-          <t>attack</t>
+          <t>combat_global</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="B5" t="inlineStr">
         <is>
-          <t>TbWeapon</t>
+          <t>TbAttack</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Weapon</t>
+          <t>Attack</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -630,7 +630,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Weapon@Gameplay.xlsx</t>
+          <t>Attack@Gameplay.xlsx</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -640,24 +640,24 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>武器数值（攻击距离/弹药/冷却/弹速/散布）</t>
+          <t>所有招式数值（玩家/敌人共用，主键=AttackData 的稳定 attackId）</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>weapon</t>
+          <t>attack</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="B6" t="inlineStr">
         <is>
-          <t>TbWeaponUpgrade</t>
+          <t>TbWeapon</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>WeaponUpgrade</t>
+          <t>Weapon</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -667,34 +667,34 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>WeaponUpgrade@Gameplay.xlsx</t>
+          <t>Weapon@Gameplay.xlsx</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>one</t>
+          <t>map</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>武器升级上限与系数（单行表）</t>
+          <t>武器数值（攻击距离/弹药/冷却/弹速/散布）</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>weapon_upgrade</t>
+          <t>weapon</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="B7" t="inlineStr">
         <is>
-          <t>TbItem</t>
+          <t>TbWeaponUpgrade</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Item</t>
+          <t>WeaponUpgrade</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -704,34 +704,34 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Item@Gameplay.xlsx</t>
+          <t>WeaponUpgrade@Gameplay.xlsx</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>map</t>
+          <t>one</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>物品与武器基础数值（背包/商店/伤害链路共用）</t>
+          <t>武器升级上限与系数（单行表）</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>item</t>
+          <t>weapon_upgrade</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="B8" t="inlineStr">
         <is>
-          <t>TbCharacter</t>
+          <t>TbItem</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Character</t>
+          <t>Item</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -741,7 +741,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Character@Gameplay.xlsx</t>
+          <t>Item@Gameplay.xlsx</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -751,24 +751,24 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>角色基础生命（玩家/敌人/Boss 共用，主键=角色配置ID）</t>
+          <t>物品与武器基础数值（背包/商店/伤害链路共用）</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>character</t>
+          <t>item</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="B9" t="inlineStr">
         <is>
-          <t>TbPlayer</t>
+          <t>TbCharacter</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Player</t>
+          <t>Character</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -778,7 +778,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Player@Gameplay.xlsx</t>
+          <t>Character@Gameplay.xlsx</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -788,24 +788,24 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>玩家移动/翻滚/锁定手感数值</t>
+          <t>角色基础生命（玩家/敌人/Boss 共用，主键=角色配置ID）</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>player</t>
+          <t>character</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="B10" t="inlineStr">
         <is>
-          <t>TbStamina</t>
+          <t>TbPlayer</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Stamina</t>
+          <t>Player</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -815,7 +815,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Stamina@Gameplay.xlsx</t>
+          <t>Player@Gameplay.xlsx</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -825,47 +825,84 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>耐力配置（玩家/敌人共用，主键引用 Character.id）</t>
+          <t>玩家移动/翻滚/锁定手感数值</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>stamina</t>
+          <t>player</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="B11" t="inlineStr">
         <is>
+          <t>TbStamina</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Stamina</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Stamina@Gameplay.xlsx</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>map</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>耐力配置（玩家/敌人共用，主键引用 Character.id）</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>stamina</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="B12" t="inlineStr">
+        <is>
           <t>TbParry</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="C12" t="inlineStr">
         <is>
           <t>Parry</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
+      <c r="D12" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="E12" t="inlineStr">
         <is>
           <t>Parry@Gameplay.xlsx</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr">
+      <c r="G12" t="inlineStr">
         <is>
           <t>map</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr">
+      <c r="I12" t="inlineStr">
         <is>
           <t>弹反/格挡数值（未启用功能的开发初始值）</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr">
+      <c r="K12" t="inlineStr">
         <is>
           <t>parry</t>
         </is>

--- a/Config/Luban/Datas/__tables__.xlsx
+++ b/Config/Luban/Datas/__tables__.xlsx
@@ -416,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K12"/>
+  <dimension ref="A1:K13"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col width="20.375" customWidth="1" style="2" min="2" max="2"/>
@@ -575,12 +575,12 @@
     <row r="4">
       <c r="B4" t="inlineStr">
         <is>
-          <t>TbCombatGlobal</t>
+          <t>TbEnemy</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>CombatGlobal</t>
+          <t>Enemy</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -590,37 +590,37 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>CombatGlobal@Gameplay.xlsx</t>
+          <t>Enemy@Gameplay.xlsx</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>one</t>
+          <t>map</t>
         </is>
       </c>
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr">
         <is>
-          <t>全局战斗默认值：兜底伤害与卡肉参数（单行表）</t>
+          <t>普通敌人控制器与 FSM 数值（主键=Character.id）</t>
         </is>
       </c>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr">
         <is>
-          <t>combat_global</t>
+          <t>enemy</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="B5" t="inlineStr">
         <is>
-          <t>TbAttack</t>
+          <t>TbCombatGlobal</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Attack</t>
+          <t>CombatGlobal</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -630,34 +630,34 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Attack@Gameplay.xlsx</t>
+          <t>CombatGlobal@Gameplay.xlsx</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>map</t>
+          <t>one</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>所有招式数值（玩家/敌人共用，主键=AttackData 的稳定 attackId）</t>
+          <t>全局战斗默认值：兜底伤害与卡肉参数（单行表）</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>attack</t>
+          <t>combat_global</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="B6" t="inlineStr">
         <is>
-          <t>TbWeapon</t>
+          <t>TbAttack</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Weapon</t>
+          <t>Attack</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -667,7 +667,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Weapon@Gameplay.xlsx</t>
+          <t>Attack@Gameplay.xlsx</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -677,24 +677,24 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>武器数值（攻击距离/弹药/冷却/弹速/散布）</t>
+          <t>所有招式数值（玩家/敌人共用，主键=AttackData 的稳定 attackId）</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>weapon</t>
+          <t>attack</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="B7" t="inlineStr">
         <is>
-          <t>TbWeaponUpgrade</t>
+          <t>TbWeapon</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>WeaponUpgrade</t>
+          <t>Weapon</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -704,34 +704,34 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>WeaponUpgrade@Gameplay.xlsx</t>
+          <t>Weapon@Gameplay.xlsx</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>one</t>
+          <t>map</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>武器升级上限与系数（单行表）</t>
+          <t>武器数值（攻击距离/弹药/冷却/弹速/散布）</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>weapon_upgrade</t>
+          <t>weapon</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="B8" t="inlineStr">
         <is>
-          <t>TbItem</t>
+          <t>TbWeaponUpgrade</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Item</t>
+          <t>WeaponUpgrade</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -741,34 +741,34 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Item@Gameplay.xlsx</t>
+          <t>WeaponUpgrade@Gameplay.xlsx</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>map</t>
+          <t>one</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>物品与武器基础数值（背包/商店/伤害链路共用）</t>
+          <t>武器升级上限与系数（单行表）</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>item</t>
+          <t>weapon_upgrade</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="B9" t="inlineStr">
         <is>
-          <t>TbCharacter</t>
+          <t>TbItem</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Character</t>
+          <t>Item</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -778,7 +778,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Character@Gameplay.xlsx</t>
+          <t>Item@Gameplay.xlsx</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -788,24 +788,24 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>角色基础生命（玩家/敌人/Boss 共用，主键=角色配置ID）</t>
+          <t>物品与武器基础数值（背包/商店/伤害链路共用）</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>character</t>
+          <t>item</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="B10" t="inlineStr">
         <is>
-          <t>TbPlayer</t>
+          <t>TbCharacter</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Player</t>
+          <t>Character</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -815,7 +815,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Player@Gameplay.xlsx</t>
+          <t>Character@Gameplay.xlsx</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -825,24 +825,24 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>玩家移动/翻滚/锁定手感数值</t>
+          <t>角色基础生命（玩家/敌人/Boss 共用，主键=角色配置ID）</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>player</t>
+          <t>character</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="B11" t="inlineStr">
         <is>
-          <t>TbStamina</t>
+          <t>TbPlayer</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Stamina</t>
+          <t>Player</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -852,7 +852,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Stamina@Gameplay.xlsx</t>
+          <t>Player@Gameplay.xlsx</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -862,47 +862,84 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>耐力配置（玩家/敌人共用，主键引用 Character.id）</t>
+          <t>玩家移动/翻滚/锁定手感数值</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>stamina</t>
+          <t>player</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="B12" t="inlineStr">
         <is>
+          <t>TbStamina</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Stamina</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Stamina@Gameplay.xlsx</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>map</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>耐力配置（玩家/敌人共用，主键引用 Character.id）</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>stamina</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="B13" t="inlineStr">
+        <is>
           <t>TbParry</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="C13" t="inlineStr">
         <is>
           <t>Parry</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
+      <c r="D13" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
+      <c r="E13" t="inlineStr">
         <is>
           <t>Parry@Gameplay.xlsx</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr">
+      <c r="G13" t="inlineStr">
         <is>
           <t>map</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr">
+      <c r="I13" t="inlineStr">
         <is>
           <t>弹反/格挡数值（未启用功能的开发初始值）</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr">
+      <c r="K13" t="inlineStr">
         <is>
           <t>parry</t>
         </is>

--- a/Config/Luban/Datas/__tables__.xlsx
+++ b/Config/Luban/Datas/__tables__.xlsx
@@ -416,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K13"/>
+  <dimension ref="A1:K14"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col width="20.375" customWidth="1" style="2" min="2" max="2"/>
@@ -575,12 +575,12 @@
     <row r="4">
       <c r="B4" t="inlineStr">
         <is>
-          <t>TbEnemy</t>
+          <t>TbEnemyGlobal</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Enemy</t>
+          <t>EnemyGlobal</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -590,37 +590,37 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Enemy@Gameplay.xlsx</t>
+          <t>EnemyGlobal@Gameplay.xlsx</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>map</t>
+          <t>one</t>
         </is>
       </c>
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr">
         <is>
-          <t>普通敌人控制器与 FSM 数值（主键=Character.id）</t>
+          <t>敌人管理器全局出手排程（单行表）</t>
         </is>
       </c>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr">
         <is>
-          <t>enemy</t>
+          <t>enemy_global</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="B5" t="inlineStr">
         <is>
-          <t>TbCombatGlobal</t>
+          <t>TbEnemy</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>CombatGlobal</t>
+          <t>Enemy</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -630,34 +630,34 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>CombatGlobal@Gameplay.xlsx</t>
+          <t>Enemy@Gameplay.xlsx</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>one</t>
+          <t>map</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>全局战斗默认值：兜底伤害与卡肉参数（单行表）</t>
+          <t>普通敌人控制器与 FSM 数值（主键=Character.id）</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>combat_global</t>
+          <t>enemy</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="B6" t="inlineStr">
         <is>
-          <t>TbAttack</t>
+          <t>TbCombatGlobal</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Attack</t>
+          <t>CombatGlobal</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -667,34 +667,34 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Attack@Gameplay.xlsx</t>
+          <t>CombatGlobal@Gameplay.xlsx</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>map</t>
+          <t>one</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>所有招式数值（玩家/敌人共用，主键=AttackData 的稳定 attackId）</t>
+          <t>全局战斗默认值：兜底伤害与卡肉参数（单行表）</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>attack</t>
+          <t>combat_global</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="B7" t="inlineStr">
         <is>
-          <t>TbWeapon</t>
+          <t>TbAttack</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Weapon</t>
+          <t>Attack</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Weapon@Gameplay.xlsx</t>
+          <t>Attack@Gameplay.xlsx</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -714,24 +714,24 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>武器数值（攻击距离/弹药/冷却/弹速/散布）</t>
+          <t>所有招式数值（玩家/敌人共用，主键=AttackData 的稳定 attackId）</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>weapon</t>
+          <t>attack</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="B8" t="inlineStr">
         <is>
-          <t>TbWeaponUpgrade</t>
+          <t>TbWeapon</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>WeaponUpgrade</t>
+          <t>Weapon</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -741,34 +741,34 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>WeaponUpgrade@Gameplay.xlsx</t>
+          <t>Weapon@Gameplay.xlsx</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>one</t>
+          <t>map</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>武器升级上限与系数（单行表）</t>
+          <t>武器数值（攻击距离/弹药/冷却/弹速/散布）</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>weapon_upgrade</t>
+          <t>weapon</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="B9" t="inlineStr">
         <is>
-          <t>TbItem</t>
+          <t>TbWeaponUpgrade</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Item</t>
+          <t>WeaponUpgrade</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -778,34 +778,34 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Item@Gameplay.xlsx</t>
+          <t>WeaponUpgrade@Gameplay.xlsx</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>map</t>
+          <t>one</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>物品与武器基础数值（背包/商店/伤害链路共用）</t>
+          <t>武器升级上限与系数（单行表）</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>item</t>
+          <t>weapon_upgrade</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="B10" t="inlineStr">
         <is>
-          <t>TbCharacter</t>
+          <t>TbItem</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Character</t>
+          <t>Item</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -815,7 +815,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Character@Gameplay.xlsx</t>
+          <t>Item@Gameplay.xlsx</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -825,24 +825,24 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>角色基础生命（玩家/敌人/Boss 共用，主键=角色配置ID）</t>
+          <t>物品与武器基础数值（背包/商店/伤害链路共用）</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>character</t>
+          <t>item</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="B11" t="inlineStr">
         <is>
-          <t>TbPlayer</t>
+          <t>TbCharacter</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Player</t>
+          <t>Character</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -852,7 +852,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Player@Gameplay.xlsx</t>
+          <t>Character@Gameplay.xlsx</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -862,24 +862,24 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>玩家移动/翻滚/锁定手感数值</t>
+          <t>角色基础生命（玩家/敌人/Boss 共用，主键=角色配置ID）</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>player</t>
+          <t>character</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="B12" t="inlineStr">
         <is>
-          <t>TbStamina</t>
+          <t>TbPlayer</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Stamina</t>
+          <t>Player</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -889,7 +889,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Stamina@Gameplay.xlsx</t>
+          <t>Player@Gameplay.xlsx</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -899,47 +899,84 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>耐力配置（玩家/敌人共用，主键引用 Character.id）</t>
+          <t>玩家移动/翻滚/锁定手感数值</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>stamina</t>
+          <t>player</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="B13" t="inlineStr">
         <is>
+          <t>TbStamina</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Stamina</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Stamina@Gameplay.xlsx</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>map</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>耐力配置（玩家/敌人共用，主键引用 Character.id）</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>stamina</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="B14" t="inlineStr">
+        <is>
           <t>TbParry</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
+      <c r="C14" t="inlineStr">
         <is>
           <t>Parry</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
         <is>
           <t>Parry@Gameplay.xlsx</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr">
+      <c r="G14" t="inlineStr">
         <is>
           <t>map</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr">
+      <c r="I14" t="inlineStr">
         <is>
           <t>弹反/格挡数值（未启用功能的开发初始值）</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr">
+      <c r="K14" t="inlineStr">
         <is>
           <t>parry</t>
         </is>

--- a/Config/Luban/Datas/__tables__.xlsx
+++ b/Config/Luban/Datas/__tables__.xlsx
@@ -416,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K14"/>
+  <dimension ref="A1:K15"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col width="20.375" customWidth="1" style="2" min="2" max="2"/>
@@ -575,12 +575,12 @@
     <row r="4">
       <c r="B4" t="inlineStr">
         <is>
-          <t>TbEnemyGlobal</t>
+          <t>TbBossPhase</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>EnemyGlobal</t>
+          <t>BossPhase</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -590,37 +590,37 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>EnemyGlobal@Gameplay.xlsx</t>
+          <t>BossPhase@Gameplay.xlsx</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>one</t>
+          <t>list</t>
         </is>
       </c>
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr">
         <is>
-          <t>敌人管理器全局出手排程（单行表）</t>
+          <t>Boss 阶段阈值（联合主键 boss_id+phase_index，当前工程无 Boss 实例故为空表）</t>
         </is>
       </c>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr">
         <is>
-          <t>enemy_global</t>
+          <t>boss_phase</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="B5" t="inlineStr">
         <is>
-          <t>TbEnemy</t>
+          <t>TbEnemyGlobal</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Enemy</t>
+          <t>EnemyGlobal</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -630,34 +630,34 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Enemy@Gameplay.xlsx</t>
+          <t>EnemyGlobal@Gameplay.xlsx</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>map</t>
+          <t>one</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>普通敌人控制器与 FSM 数值（主键=Character.id）</t>
+          <t>敌人管理器全局出手排程（单行表）</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>enemy</t>
+          <t>enemy_global</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="B6" t="inlineStr">
         <is>
-          <t>TbCombatGlobal</t>
+          <t>TbEnemy</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>CombatGlobal</t>
+          <t>Enemy</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -667,34 +667,34 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>CombatGlobal@Gameplay.xlsx</t>
+          <t>Enemy@Gameplay.xlsx</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>one</t>
+          <t>map</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>全局战斗默认值：兜底伤害与卡肉参数（单行表）</t>
+          <t>普通敌人控制器与 FSM 数值（主键=Character.id）</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>combat_global</t>
+          <t>enemy</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="B7" t="inlineStr">
         <is>
-          <t>TbAttack</t>
+          <t>TbCombatGlobal</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Attack</t>
+          <t>CombatGlobal</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -704,34 +704,34 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Attack@Gameplay.xlsx</t>
+          <t>CombatGlobal@Gameplay.xlsx</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>map</t>
+          <t>one</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>所有招式数值（玩家/敌人共用，主键=AttackData 的稳定 attackId）</t>
+          <t>全局战斗默认值：兜底伤害与卡肉参数（单行表）</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>attack</t>
+          <t>combat_global</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="B8" t="inlineStr">
         <is>
-          <t>TbWeapon</t>
+          <t>TbAttack</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Weapon</t>
+          <t>Attack</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -741,7 +741,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Weapon@Gameplay.xlsx</t>
+          <t>Attack@Gameplay.xlsx</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -751,24 +751,24 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>武器数值（攻击距离/弹药/冷却/弹速/散布）</t>
+          <t>所有招式数值（玩家/敌人共用，主键=AttackData 的稳定 attackId）</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>weapon</t>
+          <t>attack</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="B9" t="inlineStr">
         <is>
-          <t>TbWeaponUpgrade</t>
+          <t>TbWeapon</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>WeaponUpgrade</t>
+          <t>Weapon</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -778,34 +778,34 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>WeaponUpgrade@Gameplay.xlsx</t>
+          <t>Weapon@Gameplay.xlsx</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>one</t>
+          <t>map</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>武器升级上限与系数（单行表）</t>
+          <t>武器数值（攻击距离/弹药/冷却/弹速/散布）</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>weapon_upgrade</t>
+          <t>weapon</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="B10" t="inlineStr">
         <is>
-          <t>TbItem</t>
+          <t>TbWeaponUpgrade</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Item</t>
+          <t>WeaponUpgrade</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -815,34 +815,34 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Item@Gameplay.xlsx</t>
+          <t>WeaponUpgrade@Gameplay.xlsx</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>map</t>
+          <t>one</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>物品与武器基础数值（背包/商店/伤害链路共用）</t>
+          <t>武器升级上限与系数（单行表）</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>item</t>
+          <t>weapon_upgrade</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="B11" t="inlineStr">
         <is>
-          <t>TbCharacter</t>
+          <t>TbItem</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Character</t>
+          <t>Item</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -852,7 +852,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Character@Gameplay.xlsx</t>
+          <t>Item@Gameplay.xlsx</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -862,24 +862,24 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>角色基础生命（玩家/敌人/Boss 共用，主键=角色配置ID）</t>
+          <t>物品与武器基础数值（背包/商店/伤害链路共用）</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>character</t>
+          <t>item</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="B12" t="inlineStr">
         <is>
-          <t>TbPlayer</t>
+          <t>TbCharacter</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Player</t>
+          <t>Character</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -889,7 +889,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Player@Gameplay.xlsx</t>
+          <t>Character@Gameplay.xlsx</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -899,24 +899,24 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>玩家移动/翻滚/锁定手感数值</t>
+          <t>角色基础生命（玩家/敌人/Boss 共用，主键=角色配置ID）</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>player</t>
+          <t>character</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="B13" t="inlineStr">
         <is>
-          <t>TbStamina</t>
+          <t>TbPlayer</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Stamina</t>
+          <t>Player</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -926,7 +926,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Stamina@Gameplay.xlsx</t>
+          <t>Player@Gameplay.xlsx</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -936,47 +936,84 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>耐力配置（玩家/敌人共用，主键引用 Character.id）</t>
+          <t>玩家移动/翻滚/锁定手感数值</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>stamina</t>
+          <t>player</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="B14" t="inlineStr">
         <is>
+          <t>TbStamina</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Stamina</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Stamina@Gameplay.xlsx</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>map</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>耐力配置（玩家/敌人共用，主键引用 Character.id）</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>stamina</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="B15" t="inlineStr">
+        <is>
           <t>TbParry</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
+      <c r="C15" t="inlineStr">
         <is>
           <t>Parry</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
         <is>
           <t>Parry@Gameplay.xlsx</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr">
+      <c r="G15" t="inlineStr">
         <is>
           <t>map</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr">
+      <c r="I15" t="inlineStr">
         <is>
           <t>弹反/格挡数值（未启用功能的开发初始值）</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr">
+      <c r="K15" t="inlineStr">
         <is>
           <t>parry</t>
         </is>

--- a/Config/Luban/Datas/__tables__.xlsx
+++ b/Config/Luban/Datas/__tables__.xlsx
@@ -416,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K15"/>
+  <dimension ref="A1:K16"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col width="20.375" customWidth="1" style="2" min="2" max="2"/>
@@ -573,449 +573,486 @@
       </c>
     </row>
     <row r="4">
-      <c r="B4" t="inlineStr">
+      <c r="B4" s="0" t="inlineStr">
         <is>
           <t>TbBossPhase</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="C4" s="0" t="inlineStr">
         <is>
           <t>BossPhase</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
+      <c r="D4" s="0" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="E4" s="0" t="inlineStr">
         <is>
           <t>BossPhase@Gameplay.xlsx</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr"/>
-      <c r="G4" t="inlineStr">
+      <c r="F4" s="0" t="inlineStr"/>
+      <c r="G4" s="0" t="inlineStr">
         <is>
           <t>list</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr"/>
-      <c r="I4" t="inlineStr">
+      <c r="H4" s="0" t="inlineStr"/>
+      <c r="I4" s="0" t="inlineStr">
         <is>
           <t>Boss 阶段阈值（联合主键 boss_id+phase_index，当前工程无 Boss 实例故为空表）</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr">
+      <c r="J4" s="0" t="inlineStr"/>
+      <c r="K4" s="0" t="inlineStr">
         <is>
           <t>boss_phase</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="B5" t="inlineStr">
+      <c r="B5" s="0" t="inlineStr">
         <is>
           <t>TbEnemyGlobal</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C5" s="0" t="inlineStr">
         <is>
           <t>EnemyGlobal</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
+      <c r="D5" s="0" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="E5" s="0" t="inlineStr">
         <is>
           <t>EnemyGlobal@Gameplay.xlsx</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="G5" s="0" t="inlineStr">
         <is>
           <t>one</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
+      <c r="I5" s="0" t="inlineStr">
         <is>
           <t>敌人管理器全局出手排程（单行表）</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="K5" s="0" t="inlineStr">
         <is>
           <t>enemy_global</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="B6" t="inlineStr">
+      <c r="B6" s="0" t="inlineStr">
         <is>
           <t>TbEnemy</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="C6" s="0" t="inlineStr">
         <is>
           <t>Enemy</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
+      <c r="D6" s="0" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="E6" s="0" t="inlineStr">
         <is>
           <t>Enemy@Gameplay.xlsx</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="G6" s="0" t="inlineStr">
         <is>
           <t>map</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
+      <c r="I6" s="0" t="inlineStr">
         <is>
           <t>普通敌人控制器与 FSM 数值（主键=Character.id）</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr">
+      <c r="K6" s="0" t="inlineStr">
         <is>
           <t>enemy</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="B7" t="inlineStr">
+      <c r="B7" s="0" t="inlineStr">
         <is>
           <t>TbCombatGlobal</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="C7" s="0" t="inlineStr">
         <is>
           <t>CombatGlobal</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
+      <c r="D7" s="0" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="E7" s="0" t="inlineStr">
         <is>
           <t>CombatGlobal@Gameplay.xlsx</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="G7" s="0" t="inlineStr">
         <is>
           <t>one</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
+      <c r="I7" s="0" t="inlineStr">
         <is>
           <t>全局战斗默认值：兜底伤害与卡肉参数（单行表）</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr">
+      <c r="K7" s="0" t="inlineStr">
         <is>
           <t>combat_global</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="B8" t="inlineStr">
+      <c r="B8" s="0" t="inlineStr">
         <is>
           <t>TbAttack</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="C8" s="0" t="inlineStr">
         <is>
           <t>Attack</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
+      <c r="D8" s="0" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="E8" s="0" t="inlineStr">
         <is>
           <t>Attack@Gameplay.xlsx</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="G8" s="0" t="inlineStr">
         <is>
           <t>map</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr">
+      <c r="I8" s="0" t="inlineStr">
         <is>
           <t>所有招式数值（玩家/敌人共用，主键=AttackData 的稳定 attackId）</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr">
+      <c r="K8" s="0" t="inlineStr">
         <is>
           <t>attack</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="B9" t="inlineStr">
+      <c r="B9" s="0" t="inlineStr">
         <is>
           <t>TbWeapon</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="C9" s="0" t="inlineStr">
         <is>
           <t>Weapon</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
+      <c r="D9" s="0" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="E9" s="0" t="inlineStr">
         <is>
           <t>Weapon@Gameplay.xlsx</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="G9" s="0" t="inlineStr">
         <is>
           <t>map</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr">
+      <c r="I9" s="0" t="inlineStr">
         <is>
           <t>武器数值（攻击距离/弹药/冷却/弹速/散布）</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr">
+      <c r="K9" s="0" t="inlineStr">
         <is>
           <t>weapon</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="B10" t="inlineStr">
+      <c r="B10" s="0" t="inlineStr">
         <is>
           <t>TbWeaponUpgrade</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="C10" s="0" t="inlineStr">
         <is>
           <t>WeaponUpgrade</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
+      <c r="D10" s="0" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="E10" s="0" t="inlineStr">
         <is>
           <t>WeaponUpgrade@Gameplay.xlsx</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
+      <c r="G10" s="0" t="inlineStr">
         <is>
           <t>one</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr">
+      <c r="I10" s="0" t="inlineStr">
         <is>
           <t>武器升级上限与系数（单行表）</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr">
+      <c r="K10" s="0" t="inlineStr">
         <is>
           <t>weapon_upgrade</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="B11" t="inlineStr">
+      <c r="B11" s="0" t="inlineStr">
         <is>
           <t>TbItem</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="C11" s="0" t="inlineStr">
         <is>
           <t>Item</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
+      <c r="D11" s="0" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="E11" s="0" t="inlineStr">
         <is>
           <t>Item@Gameplay.xlsx</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr">
+      <c r="G11" s="0" t="inlineStr">
         <is>
           <t>map</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr">
+      <c r="I11" s="0" t="inlineStr">
         <is>
           <t>物品与武器基础数值（背包/商店/伤害链路共用）</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr">
+      <c r="K11" s="0" t="inlineStr">
         <is>
           <t>item</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="B12" t="inlineStr">
+      <c r="B12" s="0" t="inlineStr">
         <is>
           <t>TbCharacter</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="C12" s="0" t="inlineStr">
         <is>
           <t>Character</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
+      <c r="D12" s="0" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="E12" s="0" t="inlineStr">
         <is>
           <t>Character@Gameplay.xlsx</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr">
+      <c r="G12" s="0" t="inlineStr">
         <is>
           <t>map</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr">
+      <c r="I12" s="0" t="inlineStr">
         <is>
           <t>角色基础生命（玩家/敌人/Boss 共用，主键=角色配置ID）</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr">
+      <c r="K12" s="0" t="inlineStr">
         <is>
           <t>character</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="B13" t="inlineStr">
+      <c r="B13" s="0" t="inlineStr">
         <is>
           <t>TbPlayer</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
+      <c r="C13" s="0" t="inlineStr">
         <is>
           <t>Player</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
+      <c r="D13" s="0" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="E13" s="0" t="inlineStr">
         <is>
           <t>Player@Gameplay.xlsx</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr">
+      <c r="G13" s="0" t="inlineStr">
         <is>
           <t>map</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr">
+      <c r="I13" s="0" t="inlineStr">
         <is>
           <t>玩家移动/翻滚/锁定手感数值</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr">
+      <c r="K13" s="0" t="inlineStr">
         <is>
           <t>player</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="B14" t="inlineStr">
+      <c r="B14" s="0" t="inlineStr">
         <is>
           <t>TbStamina</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
+      <c r="C14" s="0" t="inlineStr">
         <is>
           <t>Stamina</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
+      <c r="D14" s="0" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="E14" s="0" t="inlineStr">
         <is>
           <t>Stamina@Gameplay.xlsx</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr">
+      <c r="G14" s="0" t="inlineStr">
         <is>
           <t>map</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr">
+      <c r="I14" s="0" t="inlineStr">
         <is>
           <t>耐力配置（玩家/敌人共用，主键引用 Character.id）</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr">
+      <c r="K14" s="0" t="inlineStr">
         <is>
           <t>stamina</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="B15" t="inlineStr">
+      <c r="B15" s="0" t="inlineStr">
         <is>
           <t>TbParry</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
+      <c r="C15" s="0" t="inlineStr">
         <is>
           <t>Parry</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
+      <c r="D15" s="0" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="E15" s="0" t="inlineStr">
         <is>
           <t>Parry@Gameplay.xlsx</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr">
+      <c r="G15" s="0" t="inlineStr">
         <is>
           <t>map</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr">
+      <c r="I15" s="0" t="inlineStr">
         <is>
           <t>弹反/格挡数值（未启用功能的开发初始值）</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr">
+      <c r="K15" s="0" t="inlineStr">
         <is>
           <t>parry</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>TbMana</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Mana</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Mana@Gameplay.xlsx</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>map</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>法力配置（玩家/敌人共用，主键引用 Character.id）</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>mana</t>
         </is>
       </c>
     </row>
